--- a/TalentMaster_Pelaajarekisteri_Pohja.xlsx
+++ b/TalentMaster_Pelaajarekisteri_Pohja.xlsx
@@ -53,7 +53,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -88,7 +87,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -98,11 +96,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -121,6 +114,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
@@ -130,7 +128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -160,6 +158,13 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
@@ -169,36 +174,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,15 +215,14 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -614,659 +620,662 @@
           <t>ℹ️  Muita tietoja (syntymäaika, osoite, PalloID) ei tarvita tässä — vanhempi täyttää ne suostumuslomakkeessa.</t>
         </is>
       </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="5" t="n"/>
     </row>
     <row r="4" ht="4" customHeight="1"/>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Etunimi *</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Sukunimi *</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Joukkue *</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Huoltajan sähköposti *</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>📋  OHJE SIHTEEREILLE</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>1.  Etunimi + Sukunimi = pelaajan nimi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="10" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>1.  Täytä jokainen pelaaja omalle rivilleen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>2.  Joukkue: valitse dropdownista ▼</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="F8" s="8" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>3.  Huoltajan s-posti: kutsu lähtee sinne.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="F9" s="8" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>4.  Tallenna → lataa takaisin TalentMasteriin.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="F10" s="8" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>5.  Vanhempi täyttää loput suostumuslomakkeessa.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="10" t="n"/>
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="12" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="9" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="10" t="n"/>
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="12" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="9" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="10" t="n"/>
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="12" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="9" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="10" t="n"/>
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="12" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="10" t="n"/>
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="12" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="9" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="10" t="n"/>
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="12" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="9" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="12" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="9" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="10" t="n"/>
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="12" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="9" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="9" t="n"/>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="10" t="n"/>
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="12" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="9" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="9" t="n"/>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="10" t="n"/>
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="12" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="7" t="n"/>
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="9" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="9" t="n"/>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="10" t="n"/>
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="12" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="9" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="10" t="n"/>
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="12" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="9" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="9" t="n"/>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="10" t="n"/>
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="12" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="6" t="n"/>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="7" t="n"/>
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="9" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="9" t="n"/>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="10" t="n"/>
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="12" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="6" t="n"/>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="9" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="9" t="n"/>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="10" t="n"/>
+      <c r="A39" s="11" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="12" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="6" t="n"/>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="9" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="9" t="n"/>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="10" t="n"/>
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="12" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="6" t="n"/>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="9" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="9" t="n"/>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="10" t="n"/>
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="12" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="6" t="n"/>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="9" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="9" t="n"/>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="10" t="n"/>
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="12" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="6" t="n"/>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="9" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="9" t="n"/>
-      <c r="B47" s="9" t="n"/>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="10" t="n"/>
+      <c r="A47" s="11" t="n"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="12" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="6" t="n"/>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="9" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="9" t="n"/>
-      <c r="B49" s="9" t="n"/>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="10" t="n"/>
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="12" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="9" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="9" t="n"/>
-      <c r="B51" s="9" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="10" t="n"/>
+      <c r="A51" s="11" t="n"/>
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="12" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="9" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="9" t="n"/>
-      <c r="B53" s="9" t="n"/>
-      <c r="C53" s="9" t="n"/>
-      <c r="D53" s="10" t="n"/>
+      <c r="A53" s="11" t="n"/>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="12" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="9" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="9" t="n"/>
-      <c r="B55" s="9" t="n"/>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="10" t="n"/>
+      <c r="A55" s="11" t="n"/>
+      <c r="B55" s="11" t="n"/>
+      <c r="C55" s="11" t="n"/>
+      <c r="D55" s="12" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="6" t="n"/>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="A56" s="8" t="n"/>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="9" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="9" t="n"/>
-      <c r="B57" s="9" t="n"/>
-      <c r="C57" s="9" t="n"/>
-      <c r="D57" s="10" t="n"/>
+      <c r="A57" s="11" t="n"/>
+      <c r="B57" s="11" t="n"/>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="12" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="6" t="n"/>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="9" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="9" t="n"/>
-      <c r="B59" s="9" t="n"/>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="10" t="n"/>
+      <c r="A59" s="11" t="n"/>
+      <c r="B59" s="11" t="n"/>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="12" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="6" t="n"/>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="9" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="9" t="n"/>
-      <c r="B61" s="9" t="n"/>
-      <c r="C61" s="9" t="n"/>
-      <c r="D61" s="10" t="n"/>
+      <c r="A61" s="11" t="n"/>
+      <c r="B61" s="11" t="n"/>
+      <c r="C61" s="11" t="n"/>
+      <c r="D61" s="12" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="6" t="n"/>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="A62" s="8" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="9" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="9" t="n"/>
-      <c r="B63" s="9" t="n"/>
-      <c r="C63" s="9" t="n"/>
-      <c r="D63" s="10" t="n"/>
+      <c r="A63" s="11" t="n"/>
+      <c r="B63" s="11" t="n"/>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="12" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="6" t="n"/>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="7" t="n"/>
+      <c r="A64" s="8" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="9" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="9" t="n"/>
-      <c r="B65" s="9" t="n"/>
-      <c r="C65" s="9" t="n"/>
-      <c r="D65" s="10" t="n"/>
+      <c r="A65" s="11" t="n"/>
+      <c r="B65" s="11" t="n"/>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="12" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="6" t="n"/>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="7" t="n"/>
+      <c r="A66" s="8" t="n"/>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="9" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="9" t="n"/>
-      <c r="B67" s="9" t="n"/>
-      <c r="C67" s="9" t="n"/>
-      <c r="D67" s="10" t="n"/>
+      <c r="A67" s="11" t="n"/>
+      <c r="B67" s="11" t="n"/>
+      <c r="C67" s="11" t="n"/>
+      <c r="D67" s="12" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="6" t="n"/>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="7" t="n"/>
+      <c r="A68" s="8" t="n"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="9" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="9" t="n"/>
-      <c r="B69" s="9" t="n"/>
-      <c r="C69" s="9" t="n"/>
-      <c r="D69" s="10" t="n"/>
+      <c r="A69" s="11" t="n"/>
+      <c r="B69" s="11" t="n"/>
+      <c r="C69" s="11" t="n"/>
+      <c r="D69" s="12" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="6" t="n"/>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="6" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="A70" s="8" t="n"/>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="9" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="9" t="n"/>
-      <c r="B71" s="9" t="n"/>
-      <c r="C71" s="9" t="n"/>
-      <c r="D71" s="10" t="n"/>
+      <c r="A71" s="11" t="n"/>
+      <c r="B71" s="11" t="n"/>
+      <c r="C71" s="11" t="n"/>
+      <c r="D71" s="12" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="6" t="n"/>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="A72" s="8" t="n"/>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="9" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="9" t="n"/>
-      <c r="B73" s="9" t="n"/>
-      <c r="C73" s="9" t="n"/>
-      <c r="D73" s="10" t="n"/>
+      <c r="A73" s="11" t="n"/>
+      <c r="B73" s="11" t="n"/>
+      <c r="C73" s="11" t="n"/>
+      <c r="D73" s="12" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="6" t="n"/>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="A74" s="8" t="n"/>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="9" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="9" t="n"/>
-      <c r="B75" s="9" t="n"/>
-      <c r="C75" s="9" t="n"/>
-      <c r="D75" s="10" t="n"/>
+      <c r="A75" s="11" t="n"/>
+      <c r="B75" s="11" t="n"/>
+      <c r="C75" s="11" t="n"/>
+      <c r="D75" s="12" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="6" t="n"/>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="7" t="n"/>
+      <c r="A76" s="8" t="n"/>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="8" t="n"/>
+      <c r="D76" s="9" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="9" t="n"/>
-      <c r="B77" s="9" t="n"/>
-      <c r="C77" s="9" t="n"/>
-      <c r="D77" s="10" t="n"/>
+      <c r="A77" s="11" t="n"/>
+      <c r="B77" s="11" t="n"/>
+      <c r="C77" s="11" t="n"/>
+      <c r="D77" s="12" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="6" t="n"/>
-      <c r="B78" s="6" t="n"/>
-      <c r="C78" s="6" t="n"/>
-      <c r="D78" s="7" t="n"/>
+      <c r="A78" s="8" t="n"/>
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="9" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="9" t="n"/>
-      <c r="B79" s="9" t="n"/>
-      <c r="C79" s="9" t="n"/>
-      <c r="D79" s="10" t="n"/>
+      <c r="A79" s="11" t="n"/>
+      <c r="B79" s="11" t="n"/>
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="12" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="6" t="n"/>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="6" t="n"/>
-      <c r="D80" s="7" t="n"/>
+      <c r="A80" s="8" t="n"/>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="9" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="9" t="n"/>
-      <c r="B81" s="9" t="n"/>
-      <c r="C81" s="9" t="n"/>
-      <c r="D81" s="10" t="n"/>
+      <c r="A81" s="11" t="n"/>
+      <c r="B81" s="11" t="n"/>
+      <c r="C81" s="11" t="n"/>
+      <c r="D81" s="12" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="6" t="n"/>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="6" t="n"/>
-      <c r="D82" s="7" t="n"/>
+      <c r="A82" s="8" t="n"/>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="9" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="9" t="n"/>
-      <c r="B83" s="9" t="n"/>
-      <c r="C83" s="9" t="n"/>
-      <c r="D83" s="10" t="n"/>
+      <c r="A83" s="11" t="n"/>
+      <c r="B83" s="11" t="n"/>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="12" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="6" t="n"/>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="6" t="n"/>
-      <c r="D84" s="7" t="n"/>
+      <c r="A84" s="8" t="n"/>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="9" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="9" t="n"/>
-      <c r="B85" s="9" t="n"/>
-      <c r="C85" s="9" t="n"/>
-      <c r="D85" s="10" t="n"/>
+      <c r="A85" s="11" t="n"/>
+      <c r="B85" s="11" t="n"/>
+      <c r="C85" s="11" t="n"/>
+      <c r="D85" s="12" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="6" t="n"/>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="6" t="n"/>
-      <c r="D86" s="7" t="n"/>
+      <c r="A86" s="8" t="n"/>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="9" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="9" t="n"/>
-      <c r="B87" s="9" t="n"/>
-      <c r="C87" s="9" t="n"/>
-      <c r="D87" s="10" t="n"/>
+      <c r="A87" s="11" t="n"/>
+      <c r="B87" s="11" t="n"/>
+      <c r="C87" s="11" t="n"/>
+      <c r="D87" s="12" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="6" t="n"/>
-      <c r="B88" s="6" t="n"/>
-      <c r="C88" s="6" t="n"/>
-      <c r="D88" s="7" t="n"/>
+      <c r="A88" s="8" t="n"/>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="9" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="9" t="n"/>
-      <c r="B89" s="9" t="n"/>
-      <c r="C89" s="9" t="n"/>
-      <c r="D89" s="10" t="n"/>
+      <c r="A89" s="11" t="n"/>
+      <c r="B89" s="11" t="n"/>
+      <c r="C89" s="11" t="n"/>
+      <c r="D89" s="12" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="6" t="n"/>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="6" t="n"/>
-      <c r="D90" s="7" t="n"/>
+      <c r="A90" s="8" t="n"/>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="8" t="n"/>
+      <c r="D90" s="9" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="9" t="n"/>
-      <c r="B91" s="9" t="n"/>
-      <c r="C91" s="9" t="n"/>
-      <c r="D91" s="10" t="n"/>
+      <c r="A91" s="11" t="n"/>
+      <c r="B91" s="11" t="n"/>
+      <c r="C91" s="11" t="n"/>
+      <c r="D91" s="12" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="6" t="n"/>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="A92" s="8" t="n"/>
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="9" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="9" t="n"/>
-      <c r="B93" s="9" t="n"/>
-      <c r="C93" s="9" t="n"/>
-      <c r="D93" s="10" t="n"/>
+      <c r="A93" s="11" t="n"/>
+      <c r="B93" s="11" t="n"/>
+      <c r="C93" s="11" t="n"/>
+      <c r="D93" s="12" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="6" t="n"/>
-      <c r="B94" s="6" t="n"/>
-      <c r="C94" s="6" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="A94" s="8" t="n"/>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="8" t="n"/>
+      <c r="D94" s="9" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="9" t="n"/>
-      <c r="B95" s="9" t="n"/>
-      <c r="C95" s="9" t="n"/>
-      <c r="D95" s="10" t="n"/>
+      <c r="A95" s="11" t="n"/>
+      <c r="B95" s="11" t="n"/>
+      <c r="C95" s="11" t="n"/>
+      <c r="D95" s="12" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="6" t="n"/>
-      <c r="B96" s="6" t="n"/>
-      <c r="C96" s="6" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="A96" s="8" t="n"/>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="9" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="9" t="n"/>
-      <c r="B97" s="9" t="n"/>
-      <c r="C97" s="9" t="n"/>
-      <c r="D97" s="10" t="n"/>
+      <c r="A97" s="11" t="n"/>
+      <c r="B97" s="11" t="n"/>
+      <c r="C97" s="11" t="n"/>
+      <c r="D97" s="12" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="6" t="n"/>
-      <c r="B98" s="6" t="n"/>
-      <c r="C98" s="6" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="A98" s="8" t="n"/>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="8" t="n"/>
+      <c r="D98" s="9" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="9" t="n"/>
-      <c r="B99" s="9" t="n"/>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="10" t="n"/>
+      <c r="A99" s="11" t="n"/>
+      <c r="B99" s="11" t="n"/>
+      <c r="C99" s="11" t="n"/>
+      <c r="D99" s="12" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="6" t="n"/>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="7" t="n"/>
+      <c r="A100" s="8" t="n"/>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="9" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="9" t="n"/>
-      <c r="B101" s="9" t="n"/>
-      <c r="C101" s="9" t="n"/>
-      <c r="D101" s="10" t="n"/>
+      <c r="A101" s="11" t="n"/>
+      <c r="B101" s="11" t="n"/>
+      <c r="C101" s="11" t="n"/>
+      <c r="D101" s="12" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="6" t="n"/>
-      <c r="B102" s="6" t="n"/>
-      <c r="C102" s="6" t="n"/>
-      <c r="D102" s="7" t="n"/>
+      <c r="A102" s="8" t="n"/>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="8" t="n"/>
+      <c r="D102" s="9" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="9" t="n"/>
-      <c r="B103" s="9" t="n"/>
-      <c r="C103" s="9" t="n"/>
-      <c r="D103" s="10" t="n"/>
+      <c r="A103" s="11" t="n"/>
+      <c r="B103" s="11" t="n"/>
+      <c r="C103" s="11" t="n"/>
+      <c r="D103" s="12" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="6" t="n"/>
-      <c r="B104" s="6" t="n"/>
-      <c r="C104" s="6" t="n"/>
-      <c r="D104" s="7" t="n"/>
+      <c r="A104" s="8" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="8" t="n"/>
+      <c r="D104" s="9" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="9" t="n"/>
-      <c r="B105" s="9" t="n"/>
-      <c r="C105" s="9" t="n"/>
-      <c r="D105" s="10" t="n"/>
+      <c r="A105" s="11" t="n"/>
+      <c r="B105" s="11" t="n"/>
+      <c r="C105" s="11" t="n"/>
+      <c r="D105" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1275,7 +1284,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C6:C105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tuntematon joukkue" error="Valitse joukkue listasta. Joukkueet löytyvät Asetukset-välilehdeltä." type="list">
+    <dataValidation sqref="C6:C105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tuntematon joukkue" error="Valitse joukkue listasta (Asetukset-välilehti)." type="list">
       <formula1>=Asetukset!$A$2:$A$30</formula1>
     </dataValidation>
   </dataValidations>
@@ -1297,123 +1306,111 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Seuran joukkueet</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
-        <is>
-          <t>← TalentMaster täyttää joukkueet automaattisesti. Älä muokkaa käsin.</t>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>← TalentMaster kirjoittaa joukkueet automaattisesti tänne latauksen yhteydessä.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>Esimerkki U10</t>
-        </is>
-      </c>
+      <c r="A2" s="15" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Esimerkki U12</t>
-        </is>
-      </c>
+      <c r="A3" s="16" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Esimerkki U15</t>
-        </is>
-      </c>
+      <c r="A4" s="15" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="14" t="inlineStr"/>
+      <c r="A5" s="16" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="13" t="inlineStr"/>
+      <c r="A6" s="15" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="14" t="inlineStr"/>
+      <c r="A7" s="16" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="13" t="inlineStr"/>
+      <c r="A8" s="15" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="14" t="inlineStr"/>
+      <c r="A9" s="16" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="13" t="inlineStr"/>
+      <c r="A10" s="15" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="14" t="inlineStr"/>
+      <c r="A11" s="16" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="13" t="inlineStr"/>
+      <c r="A12" s="15" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="14" t="inlineStr"/>
+      <c r="A13" s="16" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="13" t="inlineStr"/>
+      <c r="A14" s="15" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="14" t="inlineStr"/>
+      <c r="A15" s="16" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="13" t="inlineStr"/>
+      <c r="A16" s="15" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="14" t="inlineStr"/>
+      <c r="A17" s="16" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="13" t="inlineStr"/>
+      <c r="A18" s="15" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="14" t="inlineStr"/>
+      <c r="A19" s="16" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="13" t="inlineStr"/>
+      <c r="A20" s="15" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="14" t="inlineStr"/>
+      <c r="A21" s="16" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="13" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="14" t="inlineStr"/>
+      <c r="A23" s="16" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="13" t="inlineStr"/>
+      <c r="A24" s="15" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="14" t="inlineStr"/>
+      <c r="A25" s="16" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="13" t="inlineStr"/>
+      <c r="A26" s="15" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="14" t="inlineStr"/>
+      <c r="A27" s="16" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="13" t="inlineStr"/>
+      <c r="A28" s="15" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="14" t="inlineStr"/>
+      <c r="A29" s="16" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="13" t="inlineStr"/>
+      <c r="A30" s="15" t="inlineStr"/>
     </row>
     <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>ℹ️  Tämä välilehti täytetään automaattisesti kun lataat pohjan TalentMaster-järjestelmästä. Jos lataat pohjan suoraan GitHubista, kirjoita seuran joukkueet käsin riveille 2–30.</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n"/>
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>ℹ️  Tämä välilehti täytetään automaattisesti kun lataat pohjan TalentMaster-järjestelmästä. Jos lataat pohjan suoraan GitHubista ilman järjestelmää, kirjoita seuran joukkueet käsin riveille 2–30.</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1439,60 +1436,60 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Esimerkki täytetystä rivistä</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Etunimi *</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Sukunimi *</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Joukkue *</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Huoltajan sähköposti *</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Mikko</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>Korhonen</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>KPV U13</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>matti.korhonen@email.fi</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Huom: syntymäaika, osoite ja muut lisätiedot eivät kuulu tähän tiedostoon. Vanhempi täyttää kaikki henkilötiedot suostumuslomakkeessa.</t>
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Huom: syntymäaika, osoite ja muut tiedot eivät kuulu tähän — vanhempi täyttää ne suostumuslomakkeessa.</t>
         </is>
       </c>
     </row>
